--- a/daily_matches/job_matches_2026-09-08.xlsx
+++ b/daily_matches/job_matches_2026-09-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>London, WV, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Synapse, Dataflow, CI/CD, Git, Databricks, PySpark, Kafka, Power BI, Python</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1050647a13a073f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ea59cc6b90bbb4ce</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>full stack developer/startup founder</t>
+          <t>Software Engineer II - Automation Tester</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One Way Mirror</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,2912 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764626ef7fbd666e</t>
+          <t>https://www.indeed.com/viewjob?jk=09ab7f1974e96ec0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist / Technical Analyst</t>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ae74d9bbec7bc3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4c070562b40fadc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0551cf1610cd3e9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc074dde1eb4322a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2549a1d2d9efbe16</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e25fd7b00752cec</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rosslyn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f9d3136e9a2fad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=314764cd97e82484</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b197cae8250b9573</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a36c723938805476</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f23c32deec889542</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d542e1273738b43</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5042af754bcf7596</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8c5be3ddc6ba78f</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7790753ee8825154</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1e28ccfb6277de7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e853c6e180c5204</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=637084fed8b6fbbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e2400f910adef29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9286b681021f0ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa65a81e16970cf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49a2ddefba615540</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=694c918f86ee3bc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a239919174c51706</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f79b5958b5adaeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68440e57a8835c09</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36aa6194c9f772b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acdbc84dff5f9e6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c97efbe67728bd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5c18007250dfa99</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b743038484a91447</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c4e8ab8be1fb349</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a89004287f85f523</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=068f57df15b225f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>Chicago, IL, US USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96e78519f5c3be5f</t>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4ae502b983938a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d4c70ab5c802b0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34fc70d73aea7e13</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62d81e8597beebea</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2027 Future Talent Program - AI/ML Computational Toxicology - Intern</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Merck</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>West Point, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, spaCy, NLTK, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b654bbb7b754f7c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2027 Summer Intern - Software Engineering</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MISO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08a5f9785ebf6281</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Intern - Software Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d79a153df157a2a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer (Python, AI Agents &amp; Automation)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Burlington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a15dd66e12319b4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer (Python, AI Agents &amp; Automation)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Arizona City, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=216d37f93c8ccda8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2027 Future Talent Program - Computer Scientist - Agentic &amp; Augmented Authoring Systems - Co-op</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Merck</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>West Point, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edbe618c0a56a226</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=324c64f617a48f5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77264fd852102457</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5a8e60d936f89f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88153cdf9699fc9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a107665cc86bf38</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe78e28e1ca343a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6119895a500f743</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c493bd7f4ea8fa57</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7a52610f82b3390</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07913c8cbac58bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1da9027d5e1c61b</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54373d6510501536</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9587ef341a1c8fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afe178832b8a6053</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a841ecd741386a00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf53e8c7b65c056a</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6490e8e6fdaf5116</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7455ad8e96fd4b7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f7f205484ae4271</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe6603b388e87e9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6df29a8f460d1aeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=912fb80e18999539</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4acc4828c9cfea1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5e4a32e2e22494b</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00a434cfcd5dacca</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8400c06f1c089271</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=432614ee613f7a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c2248470823765c</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7065a07959ed987a</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21b8f5c186231258</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07d30ca92f79b853</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a6edc7b9f3fe031</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edf76ac4053bb112</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f5dd21c8ebcb09b</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80cb1edfc32e184a</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4d3b4719c39b7a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89812e113ec83046</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full-stack Developer with Anthropic Experience</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30682ae035ce25d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SAP AI- Associate Application Consultant</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=162c6b8cee8107c7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-08.xlsx
+++ b/daily_matches/job_matches_2026-09-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carto</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python</t>
+          <t>Generative AI, LangChain, RAG, Gemini, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9fa286e3251664d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7ddd4398f2504b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>LOJELIS US</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, S3, EC2, CI/CD, Jenkins, Git, Databricks, PostgreSQL, MongoDB, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b40149cae1024ef</t>
+          <t>https://www.indeed.com/viewjob?jk=389f31eefdd51556</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, FastAPI, Kubernetes, CI/CD, Git, Snowflake, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, MLflow, Docker, CI/CD, GitHub Actions, Git, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d342c243987526b3</t>
+          <t>https://www.indeed.com/viewjob?jk=442114a3c57e5a57</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer Remote Nationwide or Office-Based in MN/DC/NJ</t>
+          <t>Senior .Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java</t>
+          <t>LangChain, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c74278c8251ec6f</t>
+          <t>https://www.indeed.com/viewjob?jk=24127d299155c458</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Quality Engineer</t>
+          <t>Engineer II, Data (Cloud &amp; AI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Protolabs</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Maple Plain, MN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>Generative AI, RAG, Prompt Engineering, S3, Glue, Athena, CI/CD, Terraform, Git, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50167c9262a6f352</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c022ecfcaf20c6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vestmark</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Prompt Engineering, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Redshift, Kinesis, Docker, Kubernetes, Snowflake, Databricks, Redshift, Kafka, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af916b06ba63107</t>
+          <t>https://www.indeed.com/viewjob?jk=8708b9448e952fad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Agentic AI Engineer -2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Surplus Lines Stamping Office of Texas (SLTX)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pflugerville, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Pinecone, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f93062a4f5a70d</t>
+          <t>https://www.indeed.com/viewjob?jk=b1339134e3419aed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Sr. Azure Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Numonix</t>
+          <t>FSS Government Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, SQL, R, Scala</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06af47bdf0002d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c906b9319ac1927</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Developer (AI-accelerated)</t>
+          <t>Senior Python Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Global Linking Solutions</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>S3, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,2457 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695acbd11308a316</t>
+          <t>https://www.indeed.com/viewjob?jk=cd497236bc21a443</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Science and Analytics - Remote</t>
+          <t>Sr. Quality Assurance Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNFI</t>
+          <t>Broadcast Music</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f947c468dcbd787</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Long Key, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=860b23040114a8d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Data Lake, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63708421a0b32126</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Marketplace</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Midi Health</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60819bc4ae443d56</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Applied Analytics and Production Solutions - Remote</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Prompt Engineering, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c1ba4c02ffed42d</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7318de585b9240c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39a63e8d41e47b1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Montpelier, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfdc237a5ec2521a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96dbbd28de91d8d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f7a086e893f74d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92b76ff97226a6fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Middletown, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c823f162806160da</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42745e2b7d3b4f70</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86dbb6e245ef6f03</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=803cad2315014c66</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pawtucket, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21001c0e4015b94c</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=067ba8dc4ea90456</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hope Hull, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca747d14a8213963</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=100a2578e0de9a9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b27b5a5a2dbd7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7650cf6efa152d46</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fdab35fb5d301b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8d9249e36a5a6f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hot Springs Village, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9dfa47cceff7481b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Corrales, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b32034eb11b34213</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Charleston, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9451dd40e73a7e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c80a95d3d6ee6292</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de47c019dcb8f48a</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Kennesaw, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3900a08ed626684f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Augusta, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=592a07a140bc3c31</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Fremont, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d85fc6a7df757e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=012126d96bacab86</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Okemos, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25faed0ee0f87e0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4f528d7c6591cc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd1b53baaf5bb73e</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4e0147cefbb8eb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Kansas City, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be56d1f6c8fed56c</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724cac9c095efeeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>New Franken, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ad205890083815e</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6ee3ad0f2f5a12f</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e639c4f4fc356279</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0bc7bce3b199252</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d02ce8ad5ba0ffc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7e42009318b0530</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5620acaf132d6433</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85ded7658087672f</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c301099fdc12e291</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96c1789a53f8e267</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Upper Darby, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=803b2cfe22724310</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=805ba729e77c2f20</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer - UX and Frontend Design</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Rochester, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=127c5ebe225c6041</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer - Platform</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Rochester, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=200775bad05c046c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Associate AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Rochester, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac418ce880989eec</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Rochester, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75671b99beb3cf2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Rochester, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b9299634c7b2a66</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Infoblox DDI Engineer (On-site)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Glue, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13466b816344b71a</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer - Portsmouth NH</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Service Credit Union</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Portsmouth, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ccbeb4286b6d4f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Engineer III - Platform Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b4b81b7d3a7707c</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Specialist, Data Science</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Merck</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>West Point, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ebd11293b4932c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer I - Java - One Data Platform</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab4c0a9d96898422</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Advertiser Growth</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Olympia, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=42a673d0f16aaf8d</t>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d23ad729f213d43</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Data Science Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4036005758d19321</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>GCP Data Engineer with Agentic AI</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Gemini, BigQuery, Dataflow, CI/CD, BigQuery, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6033a7bc0be5dabd</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Databricks AI &amp; Governance</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Git, Snowflake, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ae1ccba4ccdafb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Advertiser Growth</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d28a99329fb20da</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Advertiser Growth</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=910f86f53d87c497</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Operations Data Engineer (On Site Only)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Zoll Medical Corporation</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=606ded7f86fcb046</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>First Bank</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Data Scientist, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ac561f368ff6514</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Bessemer Trust</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Woodbridge, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0654428e52d23ff5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer II - Amex Ads, Offers, and Dining Technology</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf2f3bfadea9e4c</t>
         </is>
       </c>
     </row>
